--- a/Nuevos DeepWins/Problem2_Checkerboard6x6/Res/Comparativa_15_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem2_Checkerboard6x6/Res/Comparativa_15_Neuronas.xlsx
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.212284</v>
+        <v>0.222632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -598,25 +598,25 @@
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.657895</v>
+        <v>0.594034</v>
       </c>
       <c r="H2" t="n">
-        <v>0.630517</v>
+        <v>0.577554</v>
       </c>
       <c r="I2" t="n">
-        <v>0.643915</v>
+        <v>0.585678</v>
       </c>
       <c r="J2" t="n">
-        <v>0.21283</v>
+        <v>0.224192</v>
       </c>
       <c r="K2" t="n">
-        <v>0.630435</v>
+        <v>0.587912</v>
       </c>
       <c r="L2" t="n">
-        <v>0.620321</v>
+        <v>0.572192</v>
       </c>
       <c r="M2" t="n">
-        <v>0.625337</v>
+        <v>0.579946</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_9.txt</t>
+          <t>_2_15_1_1790730365_17.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -682,35 +682,43 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.249982</v>
+        <v>0.218254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E3" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
         <v>200000</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0.62612</v>
+      </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>0.616646</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.621347</v>
+      </c>
       <c r="J3" t="n">
-        <v>0.249733</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>0.21993</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.621469</v>
+      </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>0.588235</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.604396</v>
+      </c>
       <c r="N3" t="n">
         <v>0.2</v>
       </c>
@@ -745,23 +753,23 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_17.txt</t>
+          <t>_2_15_1_1790730365_1.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z3" t="n">
         <v>15</v>
       </c>
       <c r="AA3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -775,7 +783,7 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.249979</v>
+        <v>0.249982</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -797,7 +805,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>0.249738</v>
+        <v>0.249734</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
@@ -838,7 +846,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_15.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_0.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -868,7 +876,7 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.249975</v>
+        <v>0.24998</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -890,7 +898,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.24974</v>
+        <v>0.249736</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
@@ -931,7 +939,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_4.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_8.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -961,7 +969,7 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.208679</v>
+        <v>0.212284</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -978,25 +986,25 @@
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.676359</v>
+        <v>0.657895</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6746529999999999</v>
+        <v>0.630517</v>
       </c>
       <c r="I6" t="n">
-        <v>0.675505</v>
+        <v>0.643915</v>
       </c>
       <c r="J6" t="n">
-        <v>0.209118</v>
+        <v>0.21283</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65445</v>
+        <v>0.630435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.668449</v>
+        <v>0.620321</v>
       </c>
       <c r="M6" t="n">
-        <v>0.661376</v>
+        <v>0.625337</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1032,7 +1040,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_10.txt</t>
+          <t>_2_15_1_1790730365_9.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1062,7 +1070,7 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.249981</v>
+        <v>0.249979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1084,7 +1092,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.249735</v>
+        <v>0.249737</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
@@ -1125,7 +1133,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_7.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_6.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1155,7 +1163,7 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.238832</v>
+        <v>0.222105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1172,25 +1180,25 @@
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5716290000000001</v>
+        <v>0.59199</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5132409999999999</v>
+        <v>0.596469</v>
       </c>
       <c r="I8" t="n">
-        <v>0.540864</v>
+        <v>0.594221</v>
       </c>
       <c r="J8" t="n">
-        <v>0.241796</v>
+        <v>0.223079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5397729999999999</v>
+        <v>0.586021</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5080209999999999</v>
+        <v>0.582888</v>
       </c>
       <c r="M8" t="n">
-        <v>0.523416</v>
+        <v>0.58445</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1226,7 +1234,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_2.txt</t>
+          <t>_2_15_1_1790730365_14.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1256,35 +1264,43 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.249983</v>
+        <v>0.217239</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E9" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
         <v>200000</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>0.623306</v>
+      </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>0.580076</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.6009139999999999</v>
+      </c>
       <c r="J9" t="n">
-        <v>0.249732</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>0.217696</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.621469</v>
+      </c>
       <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>0.588235</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.604396</v>
+      </c>
       <c r="N9" t="n">
         <v>0.2</v>
       </c>
@@ -1319,23 +1335,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_18.txt</t>
+          <t>_2_15_1_1790730365_18.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>15</v>
       </c>
       <c r="AA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1349,35 +1365,43 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.249972</v>
+        <v>0.224504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E10" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F10" t="n">
         <v>200000</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0.58264</v>
+      </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>0.617907</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.599755</v>
+      </c>
       <c r="J10" t="n">
-        <v>0.249747</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0.226759</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5219510000000001</v>
+      </c>
       <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+        <v>0.572192</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.545918</v>
+      </c>
       <c r="N10" t="n">
         <v>0.2</v>
       </c>
@@ -1412,23 +1436,23 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_10.txt</t>
+          <t>_2_15_1_1790730365_7.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z10" t="n">
         <v>15</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1442,7 +1466,7 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.249978</v>
+        <v>0.249972</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1464,7 +1488,7 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0.24974</v>
+        <v>0.249747</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
@@ -1505,7 +1529,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_19.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_10.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1535,43 +1559,35 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.220123</v>
+        <v>0.249975</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.62093</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.673392</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.646098</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>0.222504</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.568075</v>
-      </c>
+        <v>0.249748</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.6470590000000001</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.605</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>0.2</v>
       </c>
@@ -1606,23 +1622,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_0.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_16.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>15</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1636,7 +1652,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.24998</v>
+        <v>0.249995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1658,7 +1674,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.249736</v>
+        <v>0.249719</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
@@ -1699,7 +1715,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_13.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_3.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1729,7 +1745,7 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.21406</v>
+        <v>0.213021</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1746,25 +1762,25 @@
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.644556</v>
+        <v>0.6581630000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.649433</v>
+        <v>0.650694</v>
       </c>
       <c r="I14" t="n">
-        <v>0.646985</v>
+        <v>0.654407</v>
       </c>
       <c r="J14" t="n">
-        <v>0.215814</v>
+        <v>0.214259</v>
       </c>
       <c r="K14" t="n">
-        <v>0.645503</v>
+        <v>0.6473680000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.652406</v>
+        <v>0.6577539999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.648936</v>
+        <v>0.65252</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1800,7 +1816,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_6.txt</t>
+          <t>_2_15_1_1790730365_15.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1830,43 +1846,35 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.217239</v>
+        <v>0.249978</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.623306</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.580076</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6009139999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.217696</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.621469</v>
-      </c>
+        <v>0.249738</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0.588235</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.604396</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>0.2</v>
       </c>
@@ -1901,23 +1909,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_18.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_2.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>15</v>
       </c>
       <c r="AA15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1931,43 +1939,35 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.224504</v>
+        <v>0.249979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E16" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F16" t="n">
         <v>200000</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.58264</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.617907</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.599755</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>0.226759</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.5219510000000001</v>
-      </c>
+        <v>0.249738</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0.572192</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.545918</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>0.2</v>
       </c>
@@ -2002,23 +2002,23 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_7.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_15.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z16" t="n">
         <v>15</v>
       </c>
       <c r="AA16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2032,43 +2032,35 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.222105</v>
+        <v>0.249978</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E17" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F17" t="n">
         <v>200000</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.59199</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.596469</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.594221</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>0.223079</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.586021</v>
-      </c>
+        <v>0.249738</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.582888</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.58445</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>0.2</v>
       </c>
@@ -2103,23 +2095,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_14.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_11.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z17" t="n">
         <v>15</v>
       </c>
       <c r="AA17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2133,7 +2125,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.24998</v>
+        <v>0.249978</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2155,7 +2147,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>0.249736</v>
+        <v>0.24974</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
@@ -2196,7 +2188,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_1.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_19.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2226,7 +2218,7 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.212283</v>
+        <v>0.220123</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2243,25 +2235,25 @@
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.659004</v>
+        <v>0.62093</v>
       </c>
       <c r="H19" t="n">
-        <v>0.650694</v>
+        <v>0.673392</v>
       </c>
       <c r="I19" t="n">
-        <v>0.654822</v>
+        <v>0.646098</v>
       </c>
       <c r="J19" t="n">
-        <v>0.213909</v>
+        <v>0.222504</v>
       </c>
       <c r="K19" t="n">
-        <v>0.645161</v>
+        <v>0.568075</v>
       </c>
       <c r="L19" t="n">
-        <v>0.641711</v>
+        <v>0.6470590000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.643432</v>
+        <v>0.605</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2297,7 +2289,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_12.txt</t>
+          <t>_2_15_1_1790730365_0.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2327,7 +2319,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.249978</v>
+        <v>0.249981</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2349,7 +2341,7 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>0.249738</v>
+        <v>0.249735</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
@@ -2390,7 +2382,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_2.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_7.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2420,7 +2412,7 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.249975</v>
+        <v>0.24998</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2442,7 +2434,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>0.249748</v>
+        <v>0.249736</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
@@ -2483,7 +2475,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_16.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_13.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2513,7 +2505,7 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.212881</v>
+        <v>0.213751</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2530,25 +2522,25 @@
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.670984</v>
+        <v>0.658945</v>
       </c>
       <c r="H22" t="n">
-        <v>0.653216</v>
+        <v>0.645649</v>
       </c>
       <c r="I22" t="n">
-        <v>0.661981</v>
+        <v>0.6522289999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.213997</v>
+        <v>0.21628</v>
       </c>
       <c r="K22" t="n">
-        <v>0.657459</v>
+        <v>0.643979</v>
       </c>
       <c r="L22" t="n">
-        <v>0.636364</v>
+        <v>0.6577539999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.646739</v>
+        <v>0.650794</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2584,7 +2576,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_11.txt</t>
+          <t>_2_15_1_1790730365_13.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2614,7 +2606,7 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.249978</v>
+        <v>0.249975</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2636,7 +2628,7 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>0.249736</v>
+        <v>0.24974</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
@@ -2677,7 +2669,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_9.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_4.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2707,43 +2699,35 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.217195</v>
+        <v>0.24998</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E24" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F24" t="n">
         <v>200000</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.618031</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.656999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.636919</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>0.217516</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.610837</v>
-      </c>
+        <v>0.249736</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0.663102</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.635897</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
         <v>0.2</v>
       </c>
@@ -2778,23 +2762,23 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_8.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_1.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z24" t="n">
         <v>15</v>
       </c>
       <c r="AA24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -2909,35 +2893,43 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.249985</v>
+        <v>0.212283</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E26" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0.659004</v>
+      </c>
       <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>0.650694</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.654822</v>
+      </c>
       <c r="J26" t="n">
-        <v>0.249729</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
+        <v>0.213909</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.645161</v>
+      </c>
       <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
+        <v>0.641711</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.643432</v>
+      </c>
       <c r="N26" t="n">
         <v>0.2</v>
       </c>
@@ -2972,23 +2964,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_14.txt</t>
+          <t>_2_15_1_1790730365_12.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>15</v>
       </c>
       <c r="AA26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3002,43 +2994,35 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.198838</v>
+        <v>0.249985</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E27" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F27" t="n">
         <v>200000</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.690883</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.611602</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.648829</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>0.213137</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.630952</v>
-      </c>
+        <v>0.249729</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>0.566845</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.597183</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>0.2</v>
       </c>
@@ -3073,23 +3057,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_16.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_14.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z27" t="n">
         <v>15</v>
       </c>
       <c r="AA27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3103,35 +3087,43 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.249981</v>
+        <v>0.208679</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E28" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
         <v>200000</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>0.676359</v>
+      </c>
       <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>0.6746529999999999</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.675505</v>
+      </c>
       <c r="J28" t="n">
-        <v>0.249735</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
+        <v>0.209118</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.65445</v>
+      </c>
       <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr"/>
+        <v>0.668449</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.661376</v>
+      </c>
       <c r="N28" t="n">
         <v>0.2</v>
       </c>
@@ -3166,23 +3158,23 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_5.txt</t>
+          <t>_2_15_1_1790730365_10.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z28" t="n">
         <v>15</v>
       </c>
       <c r="AA28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3196,35 +3188,43 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.249995</v>
+        <v>0.212881</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E29" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F29" t="n">
         <v>200000</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>0.670984</v>
+      </c>
       <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>0.653216</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.661981</v>
+      </c>
       <c r="J29" t="n">
-        <v>0.249719</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
+        <v>0.213997</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.657459</v>
+      </c>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
+        <v>0.636364</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.646739</v>
+      </c>
       <c r="N29" t="n">
         <v>0.2</v>
       </c>
@@ -3259,23 +3259,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_3.txt</t>
+          <t>_2_15_1_1790730365_11.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>15</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3289,43 +3289,35 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.213751</v>
+        <v>0.249978</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E30" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F30" t="n">
         <v>200000</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.658945</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.645649</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.6522289999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>0.21628</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.643979</v>
-      </c>
+        <v>0.249736</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>0.6577539999999999</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.650794</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>0.2</v>
       </c>
@@ -3360,23 +3352,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_13.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_9.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z30" t="n">
         <v>15</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3390,7 +3382,7 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.249978</v>
+        <v>0.249977</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3412,7 +3404,7 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>0.249738</v>
+        <v>0.24974</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
@@ -3453,7 +3445,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_11.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_12.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3483,35 +3475,43 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.249979</v>
+        <v>0.21201</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>0.651282</v>
+      </c>
       <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>0.640605</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.6459</v>
+      </c>
       <c r="J32" t="n">
-        <v>0.249737</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
+        <v>0.213267</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.625</v>
+      </c>
       <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
+        <v>0.614973</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.619946</v>
+      </c>
       <c r="N32" t="n">
         <v>0.2</v>
       </c>
@@ -3546,23 +3546,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_6.txt</t>
+          <t>_2_15_1_1790730365_3.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>15</v>
       </c>
       <c r="AA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3576,7 +3576,7 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.222632</v>
+        <v>0.198838</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3593,25 +3593,25 @@
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.594034</v>
+        <v>0.690883</v>
       </c>
       <c r="H33" t="n">
-        <v>0.577554</v>
+        <v>0.611602</v>
       </c>
       <c r="I33" t="n">
-        <v>0.585678</v>
+        <v>0.648829</v>
       </c>
       <c r="J33" t="n">
-        <v>0.224192</v>
+        <v>0.213137</v>
       </c>
       <c r="K33" t="n">
-        <v>0.587912</v>
+        <v>0.630952</v>
       </c>
       <c r="L33" t="n">
-        <v>0.572192</v>
+        <v>0.566845</v>
       </c>
       <c r="M33" t="n">
-        <v>0.579946</v>
+        <v>0.597183</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_17.txt</t>
+          <t>_2_15_1_1790730365_16.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3677,43 +3677,35 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.21201</v>
+        <v>0.249983</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E34" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F34" t="n">
         <v>200000</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.651282</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0.640605</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.6459</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>0.213267</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.625</v>
-      </c>
+        <v>0.249732</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>0.614973</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.619946</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>0.2</v>
       </c>
@@ -3748,23 +3740,23 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_3.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_18.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z34" t="n">
         <v>15</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -3778,43 +3770,35 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.218254</v>
+        <v>0.249981</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1790730365</v>
+        <v>1790730422</v>
       </c>
       <c r="E35" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F35" t="n">
         <v>200000</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.62612</v>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.616646</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.621347</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>0.21993</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.621469</v>
-      </c>
+        <v>0.249735</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>0.588235</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.604396</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>0.2</v>
       </c>
@@ -3849,23 +3833,23 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_1.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_5.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z35" t="n">
         <v>15</v>
       </c>
       <c r="AA35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -3879,7 +3863,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.249977</v>
+        <v>0.249982</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3901,7 +3885,7 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>0.24974</v>
+        <v>0.249733</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
@@ -3942,7 +3926,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_12.txt</t>
+          <t>_2_3_3_3_3_3_1_1790730422_17.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -3972,7 +3956,7 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.213021</v>
+        <v>0.238832</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -3989,25 +3973,25 @@
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.6581630000000001</v>
+        <v>0.5716290000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0.650694</v>
+        <v>0.5132409999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>0.654407</v>
+        <v>0.540864</v>
       </c>
       <c r="J37" t="n">
-        <v>0.214259</v>
+        <v>0.241796</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6473680000000001</v>
+        <v>0.5397729999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>0.6577539999999999</v>
+        <v>0.5080209999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>0.65252</v>
+        <v>0.523416</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4043,7 +4027,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_15.txt</t>
+          <t>_2_15_1_1790730365_2.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4174,35 +4158,43 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.24998</v>
+        <v>0.21406</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E39" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>0.644556</v>
+      </c>
       <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>0.649433</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.646985</v>
+      </c>
       <c r="J39" t="n">
-        <v>0.249736</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
+        <v>0.215814</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.645503</v>
+      </c>
       <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
+        <v>0.652406</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.648936</v>
+      </c>
       <c r="N39" t="n">
         <v>0.2</v>
       </c>
@@ -4237,23 +4229,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_8.txt</t>
+          <t>_2_15_1_1790730365_6.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>15</v>
       </c>
       <c r="AA39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4267,7 +4259,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.214535</v>
+        <v>0.217195</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4284,25 +4276,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.627371</v>
+        <v>0.618031</v>
       </c>
       <c r="H40" t="n">
-        <v>0.583859</v>
+        <v>0.656999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.604833</v>
+        <v>0.636919</v>
       </c>
       <c r="J40" t="n">
-        <v>0.214865</v>
+        <v>0.217516</v>
       </c>
       <c r="K40" t="n">
-        <v>0.644444</v>
+        <v>0.610837</v>
       </c>
       <c r="L40" t="n">
-        <v>0.620321</v>
+        <v>0.663102</v>
       </c>
       <c r="M40" t="n">
-        <v>0.632153</v>
+        <v>0.635897</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4338,7 +4330,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_15_1_1790730365_4.txt</t>
+          <t>_2_15_1_1790730365_8.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4368,35 +4360,43 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.249982</v>
+        <v>0.214535</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790730422</v>
+        <v>1790730365</v>
       </c>
       <c r="E41" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>0.627371</v>
+      </c>
       <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>0.583859</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.604833</v>
+      </c>
       <c r="J41" t="n">
-        <v>0.249734</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
+        <v>0.214865</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.644444</v>
+      </c>
       <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
+        <v>0.620321</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.632153</v>
+      </c>
       <c r="N41" t="n">
         <v>0.2</v>
       </c>
@@ -4431,23 +4431,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790730422_0.txt</t>
+          <t>_2_15_1_1790730365_4.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>15</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v>0.6109017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03778774413414179</v>
+        <v>0.03778774413414183</v>
       </c>
       <c r="D2" t="n">
         <v>0.661376</v>
